--- a/example/二层最大-8192卡-X400-RoCE/excel/hostname.xlsx
+++ b/example/二层最大-8192卡-X400-RoCE/excel/hostname.xlsx
@@ -428,7 +428,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H3C S9827</t>
+          <t>浪潮 X400 (Spectrum-4)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2782,7 +2782,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -3064,7 +3064,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -3578,7 +3578,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
